--- a/컨퍼런스_업로드_양식.xlsx
+++ b/컨퍼런스_업로드_양식.xlsx
@@ -640,7 +640,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:N4"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -648,12 +648,14 @@
     <col min="4" max="4" width="20.83203125" customWidth="1"/>
     <col min="5" max="5" width="20.83203125" customWidth="1"/>
     <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
     <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="12.83203125" customWidth="1"/>
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="14.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -673,24 +675,30 @@
         <v>직함(영문)</v>
       </c>
       <c r="F1" t="str">
+        <v>국적</v>
+      </c>
+      <c r="G1" t="str">
+        <v>거주지</v>
+      </c>
+      <c r="H1" t="str">
         <v>언어</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>섭외 상태</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>메일</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>전화</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>연사료</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>통화</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>메모</v>
       </c>
     </row>
@@ -711,24 +719,30 @@
         <v/>
       </c>
       <c r="F2" t="str">
+        <v>↳ 국가명 (예: 대한민국, 미국)</v>
+      </c>
+      <c r="G2" t="str">
+        <v>↳ 국적과 다를 수 있어요 — 연사료·항공을 여기 기준으로 할 때가 있습니다</v>
+      </c>
+      <c r="H2" t="str">
         <v>↳ 비움 / both(국·영문) / en(해외 연사, 영문만)</v>
       </c>
-      <c r="G2" t="str">
+      <c r="I2" t="str">
         <v>↳ 섭외중 / 확정 / 보류 / 취소 — 비우면 섭외중</v>
       </c>
-      <c r="H2" t="str">
+      <c r="J2" t="str">
         <v>↳ 적어 두면 연락 상대(수신)로 함께 만들어집니다</v>
       </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <v>↳ 숫자만 (예: 500000)</v>
       </c>
-      <c r="K2" t="str">
+      <c r="M2" t="str">
         <v>↳ KRW / USD — 비우면 KRW</v>
       </c>
-      <c r="L2" t="str">
+      <c r="N2" t="str">
         <v/>
       </c>
     </row>
@@ -749,24 +763,30 @@
         <v>Principal</v>
       </c>
       <c r="F3" t="str">
+        <v>대한민국</v>
+      </c>
+      <c r="G3" t="str">
+        <v>대한민국</v>
+      </c>
+      <c r="H3" t="str">
         <v>both</v>
       </c>
-      <c r="G3" t="str">
+      <c r="I3" t="str">
         <v>확정</v>
       </c>
-      <c r="H3" t="str">
+      <c r="J3" t="str">
         <v>chung@example.kr</v>
       </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v>500000</v>
       </c>
-      <c r="K3" t="str">
+      <c r="M3" t="str">
         <v>KRW</v>
       </c>
-      <c r="L3" t="str">
+      <c r="N3" t="str">
         <v/>
       </c>
     </row>
@@ -787,30 +807,36 @@
         <v>Founder</v>
       </c>
       <c r="F4" t="str">
+        <v>대한민국</v>
+      </c>
+      <c r="G4" t="str">
+        <v>미국</v>
+      </c>
+      <c r="H4" t="str">
         <v>en</v>
       </c>
-      <c r="G4" t="str">
+      <c r="I4" t="str">
         <v>섭외중</v>
       </c>
-      <c r="H4" t="str">
+      <c r="J4" t="str">
         <v>eric@example.com</v>
       </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
       <c r="K4" t="str">
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>해외 연사</v>
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v>국적은 한국, 거주지는 미국</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/컨퍼런스_업로드_양식.xlsx
+++ b/컨퍼런스_업로드_양식.xlsx
@@ -640,22 +640,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:O4"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
     <col min="3" max="3" width="20.83203125" customWidth="1"/>
     <col min="4" max="4" width="20.83203125" customWidth="1"/>
     <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
     <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="14.83203125" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" customWidth="1"/>
     <col min="14" max="14" width="12.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -663,42 +664,45 @@
         <v>성명</v>
       </c>
       <c r="B1" t="str">
+        <v>성명(영문)</v>
+      </c>
+      <c r="C1" t="str">
         <v>소속(국문)</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>소속(영문)</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>직함(국문)</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>직함(영문)</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>국적</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>거주지</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>언어</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>섭외 상태</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>메일</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>전화</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>연사료</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>통화</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>메모</v>
       </c>
     </row>
@@ -707,11 +711,11 @@
         <v>↳ 프로그램에 나갈 이름. 배정 시트에서 이 이름으로 찾습니다</v>
       </c>
       <c r="B2" t="str">
+        <v>↳ 해외 연사는 이 칸만 채워도 됩니다</v>
+      </c>
+      <c r="C2" t="str">
         <v>↳ 발표 당시의 소속입니다</v>
       </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
       <c r="D2" t="str">
         <v/>
       </c>
@@ -719,30 +723,33 @@
         <v/>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
         <v>↳ 국가명 (예: 대한민국, 미국)</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>↳ 국적과 다를 수 있어요 — 연사료·항공을 여기 기준으로 할 때가 있습니다</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>↳ 비움 / both(국·영문) / en(해외 연사, 영문만)</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>↳ 섭외중 / 확정 / 보류 / 취소 — 비우면 섭외중</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>↳ 적어 두면 연락 상대(수신)로 함께 만들어집니다</v>
       </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
       <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>↳ 숫자만 (예: 500000)</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>↳ KRW / USD — 비우면 KRW</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v/>
       </c>
     </row>
@@ -751,42 +758,45 @@
         <v>정청수</v>
       </c>
       <c r="B3" t="str">
+        <v>Chung-soo Jung</v>
+      </c>
+      <c r="C3" t="str">
         <v>○○건축사사무소</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>OO Architects</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>대표</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>Principal</v>
-      </c>
-      <c r="F3" t="str">
-        <v>대한민국</v>
       </c>
       <c r="G3" t="str">
         <v>대한민국</v>
       </c>
       <c r="H3" t="str">
+        <v>대한민국</v>
+      </c>
+      <c r="I3" t="str">
         <v>both</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>확정</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>chung@example.kr</v>
       </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
       <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>500000</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>KRW</v>
       </c>
-      <c r="N3" t="str">
+      <c r="O3" t="str">
         <v/>
       </c>
     </row>
@@ -798,32 +808,32 @@
         <v/>
       </c>
       <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
         <v>Studio Ho</v>
       </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
       <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
         <v>Founder</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>대한민국</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>미국</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>en</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>섭외중</v>
       </c>
-      <c r="J4" t="str">
+      <c r="K4" t="str">
         <v>eric@example.com</v>
       </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
       <c r="L4" t="str">
         <v/>
       </c>
@@ -831,12 +841,15 @@
         <v/>
       </c>
       <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
         <v>국적은 한국, 거주지는 미국</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O4"/>
   </ignoredErrors>
 </worksheet>
 </file>
